--- a/reports/executive_slides.xlsx
+++ b/reports/executive_slides.xlsx
@@ -37,12 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
   <si>
     <t xml:space="preserve">Executive deck - companion workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Every figure and table from executive_slides.Rmd, in slide order (generated 2026-08-30 16:27).</t>
+    <t xml:space="preserve">Every figure and table from executive_slides.Rmd, in slide order (generated 2026-08-31 21:28).</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">figure</t>
   </si>
   <si>
-    <t xml:space="preserve">Type-2 diabetes treatment drives most of Indonesia's clinical cardiovascular budget through 2050</t>
+    <t xml:space="preserve">Primary CVD prevention drives most of Indonesia's clinical cardiovascular budget through 2050</t>
   </si>
   <si>
     <t xml:space="preserve">fig-clin-budget</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">06_fig-clin-budget</t>
   </si>
   <si>
-    <t xml:space="preserve">Type-2 diabetes treatment still drives most of the undiscounted clinical cardiovascular budget through 2050</t>
+    <t xml:space="preserve">Primary CVD prevention still drives most of the undiscounted clinical cardiovascular budget through 2050</t>
   </si>
   <si>
     <t xml:space="preserve">fig-clin-budget-undisc</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">15_fig-casc-2panel-undisc</t>
   </si>
   <si>
-    <t xml:space="preserve">A stronger cascade could prevent about 1.6 million deaths by 2050</t>
+    <t xml:space="preserve">A stronger cascade could prevent about 1.5 million deaths by 2050</t>
   </si>
   <si>
     <t xml:space="preserve">tbl-cascade</t>
@@ -210,7 +210,7 @@
     <t xml:space="preserve">16_tbl-cascade</t>
   </si>
   <si>
-    <t xml:space="preserve">On an undiscounted basis, a stronger cascade still prevents about 1.6 million deaths by 2050</t>
+    <t xml:space="preserve">On an undiscounted basis, a stronger cascade still prevents about 1.5 million deaths by 2050</t>
   </si>
   <si>
     <t xml:space="preserve">tbl-cascade-undisc</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">17_tbl-cascade-undisc</t>
   </si>
   <si>
-    <t xml:space="preserve">Care cascade, tobacco tax, all prevention, and the full package all move Indonesia toward its neighbours</t>
+    <t xml:space="preserve">The care cascade and tobacco policies jointly move Indonesia further toward its neighbours</t>
   </si>
   <si>
     <t xml:space="preserve">fig-40q30-cascade</t>
@@ -333,18 +333,18 @@
     <t xml:space="preserve">Heart-attack (IHD) survivors</t>
   </si>
   <si>
+    <t xml:space="preserve">Acute heart-failure care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acute heart-failure patients</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chronic heart-failure care</t>
   </si>
   <si>
     <t xml:space="preserve">Chronic heart-failure patients</t>
   </si>
   <si>
-    <t xml:space="preserve">Acute heart-failure care</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acute heart-failure patients</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stroke secondary prevention</t>
   </si>
   <si>
@@ -363,24 +363,24 @@
     <t xml:space="preserve">Implementation lever</t>
   </si>
   <si>
+    <t xml:space="preserve">Tobacco tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tobacco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New cases + survival</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise tax to 75% of retail price</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tobacco policy package</t>
   </si>
   <si>
-    <t xml:space="preserve">Tobacco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New cases + survival</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clean-air law, mass media, ad ban</t>
   </si>
   <si>
-    <t xml:space="preserve">Tobacco tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raise tax to 75% of retail price</t>
-  </si>
-  <si>
     <t xml:space="preserve">TABLE  |  tbl-sources</t>
   </si>
   <si>
@@ -498,559 +498,553 @@
     <t xml:space="preserve">Add'l cost/capita in 2050 (disc.)</t>
   </si>
   <si>
-    <t xml:space="preserve">1,964,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7%</t>
+    <t xml:space="preserve">2,134,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$8,608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$2.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$3.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">458,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$15,314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$23,164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158,000</t>
   </si>
   <si>
     <t xml:space="preserve">11.5%</t>
   </si>
   <si>
-    <t xml:space="preserve">US$4,998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$1.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$1.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">493,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6%</t>
+    <t xml:space="preserve">1.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$32,038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99,000</t>
   </si>
   <si>
     <t xml:space="preserve">0.6%</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$160,079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$10.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$16.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$40,430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$1.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$2.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">244,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$20,605</t>
+    <t xml:space="preserve">US$30,783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$20,607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$109,233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All clinical (combined)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,176,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$13,014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$5.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$7.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE  |  tbl-clin-ce-undisc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per death averted (undisc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg. annual add'l cost/capita, 2026-50 (undisc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add'l cost/capita in 2050 (undisc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$14,021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$4.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$7.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$25,216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$3.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$38,092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$3.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$52,818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$2.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$50,904</t>
   </si>
   <si>
     <t xml:space="preserve">US$0.69</t>
   </si>
   <si>
-    <t xml:space="preserve">US$1.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$10,410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$24,657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$70,561</t>
+    <t xml:space="preserve">US$1.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$34,061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$178,379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$21,213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$9.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$16.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIGURE  |  fig-clin-budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIGURE  |  fig-clin-budget-undisc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE  |  tbl-ph-ce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public-health policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,453,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">650,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All public health (combined)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,071,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE  |  tbl-ph-ce-undisc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE  |  tbl-combined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduction in prob. of CVD death &lt;70, 2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discounted total cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$41.3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$323.6M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical + public health (combined)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,996,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$41.4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$8,279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$7.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE  |  tbl-combined-undisc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undiscounted total cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$67.4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$475.1M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$13,486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$16.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIGURE  |  fig-40q30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIGURE  |  fig-htn-cascade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIGURE  |  fig-casc-2panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIGURE  |  fig-casc-2panel-undisc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE  |  tbl-cascade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative from 2025 through year (unless noted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline (current course)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional cost (US$ billion, discounted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deaths prevented (million)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional cost per capita in that year (US$, discounted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$1.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE  |  tbl-cascade-undisc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional cost (US$ billion, undiscounted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional cost per capita in that year (US$, undiscounted)</t>
   </si>
   <si>
     <t xml:space="preserve">US$0.39</t>
   </si>
   <si>
-    <t xml:space="preserve">US$0.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All clinical (combined)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,153,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$34,388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$14.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$22.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABLE  |  tbl-clin-ce-undisc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost per death averted (undisc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg. annual add'l cost/capita, 2026-50 (undisc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add'l cost/capita in 2050 (undisc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$8,140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$2.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$3.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$263,582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$17.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$34.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$66,485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$2.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$5.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$33,966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$1.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$2.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$17,267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$40,773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$115,372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$1.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$56,477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$24.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$46.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIGURE  |  fig-clin-budget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIGURE  |  fig-clin-budget-undisc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABLE  |  tbl-ph-ce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public-health policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">650,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">390,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All public health (combined)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,031,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABLE  |  tbl-ph-ce-undisc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABLE  |  tbl-combined</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduction in prob. of CVD death &lt;70, 2050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discounted total cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$108.4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$323.3M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinical + public health (combined)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,063,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$107.8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$26,542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$14.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$21.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABLE  |  tbl-combined-undisc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Undiscounted total cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$178.1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$474.6M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$177.0B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$43,562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$24.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$45.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIGURE  |  fig-40q30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIGURE  |  fig-htn-cascade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIGURE  |  fig-casc-2panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIGURE  |  fig-casc-2panel-undisc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABLE  |  tbl-cascade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative from 2025 through year (unless noted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline (current course)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional cost (US$ billion, discounted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deaths prevented (million)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional cost per capita in that year (US$, discounted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$8.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$7.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABLE  |  tbl-cascade-undisc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional cost (US$ billion, undiscounted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional cost per capita in that year (US$, undiscounted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$0.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$12.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US$14.92</t>
+    <t xml:space="preserve">US$2.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$2.74</t>
   </si>
   <si>
     <t xml:space="preserve">FIGURE  |  fig-40q30-cascade</t>
@@ -1440,7 +1434,7 @@
       <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">4</xdr:row>
       <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="8778240" cy="3840480"/>
+    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="7315200" cy="5486400"/>
     <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
       <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
         <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Picture 1"/>
@@ -2515,7 +2509,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3">
@@ -2540,13 +2534,13 @@
         <v>149</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="6">
@@ -2557,22 +2551,22 @@
         <v>237</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -2580,51 +2574,51 @@
         <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -2655,7 +2649,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3">
@@ -2665,19 +2659,19 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>146</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>147</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>150</v>
@@ -2691,77 +2685,77 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" t="s">
         <v>198</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" t="s">
         <v>199</v>
       </c>
-      <c r="C6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" t="s">
-        <v>200</v>
-      </c>
       <c r="E6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F6" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" t="s">
         <v>203</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>204</v>
-      </c>
-      <c r="H6" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
         <v>252</v>
       </c>
-      <c r="D7" t="s">
-        <v>251</v>
-      </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G8" t="s">
-        <v>279</v>
+        <v>203</v>
       </c>
       <c r="H8" t="s">
         <v>280</v>
@@ -2805,13 +2799,13 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>146</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>147</v>
@@ -2820,27 +2814,27 @@
         <v>282</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" t="s">
         <v>198</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" t="s">
         <v>199</v>
-      </c>
-      <c r="C6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" t="s">
-        <v>200</v>
       </c>
       <c r="E6" t="s">
         <v>283</v>
@@ -2857,54 +2851,54 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
         <v>252</v>
-      </c>
-      <c r="D7" t="s">
-        <v>251</v>
       </c>
       <c r="E7" t="s">
         <v>284</v>
       </c>
       <c r="F7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F8" t="s">
         <v>285</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" t="s">
         <v>286</v>
-      </c>
-      <c r="G8" t="s">
-        <v>287</v>
-      </c>
-      <c r="H8" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +2919,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -2952,7 +2946,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3">
@@ -2979,7 +2973,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -3006,7 +3000,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -3039,7 +3033,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3">
@@ -3049,30 +3043,30 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" t="s">
         <v>298</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>299</v>
-      </c>
-      <c r="C6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="7">
@@ -3080,27 +3074,27 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" t="s">
         <v>302</v>
-      </c>
-      <c r="C7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D8" t="s">
         <v>305</v>
-      </c>
-      <c r="C8" t="s">
-        <v>306</v>
-      </c>
-      <c r="D8" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="9">
@@ -3108,55 +3102,55 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" t="s">
         <v>308</v>
-      </c>
-      <c r="C9" t="s">
-        <v>309</v>
-      </c>
-      <c r="D9" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" t="s">
         <v>311</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>312</v>
-      </c>
-      <c r="C10" t="s">
-        <v>313</v>
-      </c>
-      <c r="D10" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" t="s">
         <v>315</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>316</v>
-      </c>
-      <c r="C11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D11" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C12" t="s">
         <v>319</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>320</v>
-      </c>
-      <c r="C12" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" t="s">
-        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -3183,7 +3177,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3">
@@ -3193,30 +3187,30 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" t="s">
         <v>298</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>299</v>
-      </c>
-      <c r="C6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="7">
@@ -3224,27 +3218,27 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" t="s">
         <v>302</v>
-      </c>
-      <c r="C7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" t="s">
+        <v>323</v>
+      </c>
+      <c r="D8" t="s">
         <v>324</v>
-      </c>
-      <c r="C8" t="s">
-        <v>325</v>
-      </c>
-      <c r="D8" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3252,55 +3246,55 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
+        <v>325</v>
+      </c>
+      <c r="C9" t="s">
+        <v>326</v>
+      </c>
+      <c r="D9" t="s">
         <v>327</v>
-      </c>
-      <c r="C9" t="s">
-        <v>328</v>
-      </c>
-      <c r="D9" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C10" t="s">
         <v>330</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>331</v>
-      </c>
-      <c r="C10" t="s">
-        <v>332</v>
-      </c>
-      <c r="D10" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" t="s">
         <v>315</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>316</v>
-      </c>
-      <c r="C11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D11" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B12" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" t="s">
         <v>334</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>335</v>
-      </c>
-      <c r="C12" t="s">
-        <v>336</v>
-      </c>
-      <c r="D12" t="s">
-        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -3321,7 +3315,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3">
@@ -3467,7 +3461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3">
@@ -3494,7 +3488,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3">
@@ -3521,7 +3515,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3">
@@ -3548,7 +3542,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
@@ -3575,7 +3569,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3">
@@ -3602,7 +3596,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3">
@@ -3634,7 +3628,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3">
@@ -3644,65 +3638,65 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>346</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6" t="s">
         <v>349</v>
-      </c>
-      <c r="B6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C6" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" t="s">
         <v>352</v>
-      </c>
-      <c r="B7" t="s">
-        <v>353</v>
-      </c>
-      <c r="C7" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B8" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C10" t="s">
         <v>94</v>
@@ -3710,123 +3704,123 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C11" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>366</v>
+      </c>
+      <c r="B15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15" t="s">
         <v>368</v>
-      </c>
-      <c r="B15" t="s">
-        <v>369</v>
-      </c>
-      <c r="C15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B18" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B19" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C19" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B20" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C20" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>377</v>
+      </c>
+      <c r="B21" t="s">
+        <v>378</v>
+      </c>
+      <c r="C21" t="s">
         <v>379</v>
-      </c>
-      <c r="B21" t="s">
-        <v>380</v>
-      </c>
-      <c r="C21" t="s">
-        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4227,16 +4221,16 @@
         <v>182</v>
       </c>
       <c r="E10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F10" t="s">
         <v>183</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>184</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>185</v>
-      </c>
-      <c r="H10" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -4244,16 +4238,16 @@
         <v>100</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
         <v>161</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F11" t="s">
         <v>188</v>
@@ -4276,45 +4270,45 @@
         <v>192</v>
       </c>
       <c r="D12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" t="s">
         <v>193</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>194</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>195</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>196</v>
-      </c>
-      <c r="H12" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" t="s">
         <v>198</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>199</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>200</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>201</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>202</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>203</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>204</v>
-      </c>
-      <c r="H13" t="s">
-        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -4345,7 +4339,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
@@ -4370,13 +4364,13 @@
         <v>149</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="6">
@@ -4396,13 +4390,13 @@
         <v>156</v>
       </c>
       <c r="F6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" t="s">
         <v>210</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>211</v>
-      </c>
-      <c r="H6" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="7">
@@ -4422,13 +4416,13 @@
         <v>163</v>
       </c>
       <c r="F7" t="s">
+        <v>212</v>
+      </c>
+      <c r="G7" t="s">
         <v>213</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>214</v>
-      </c>
-      <c r="H7" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="8">
@@ -4448,13 +4442,13 @@
         <v>170</v>
       </c>
       <c r="F8" t="s">
+        <v>215</v>
+      </c>
+      <c r="G8" t="s">
         <v>216</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>217</v>
-      </c>
-      <c r="H8" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="9">
@@ -4474,13 +4468,13 @@
         <v>177</v>
       </c>
       <c r="F9" t="s">
+        <v>218</v>
+      </c>
+      <c r="G9" t="s">
         <v>219</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>220</v>
-      </c>
-      <c r="H9" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -4497,16 +4491,16 @@
         <v>182</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G10" t="s">
         <v>222</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>223</v>
-      </c>
-      <c r="H10" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="11">
@@ -4514,16 +4508,16 @@
         <v>100</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
         <v>161</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F11" t="s">
         <v>224</v>
@@ -4546,10 +4540,10 @@
         <v>192</v>
       </c>
       <c r="D12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" t="s">
         <v>193</v>
-      </c>
-      <c r="E12" t="s">
-        <v>194</v>
       </c>
       <c r="F12" t="s">
         <v>227</v>
@@ -4563,19 +4557,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" t="s">
         <v>198</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>199</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>200</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>201</v>
-      </c>
-      <c r="E13" t="s">
-        <v>202</v>
       </c>
       <c r="F13" t="s">
         <v>230</v>
@@ -4711,22 +4705,22 @@
         <v>237</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7">
@@ -4734,51 +4728,51 @@
         <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
